--- a/NBFC-MF/Borrowers/Angom_Bijenti_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Angom_Bijenti_Daily.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>29500</v>
+        <v>28500</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>26910.362742211062</v>
+        <v>26076.674163036809</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>23089.637257788938</v>
+        <v>23923.325836963191</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -2687,59 +2687,63 @@
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" s="19"/>
-      <c r="B63" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A63" s="19">
+        <v>46281</v>
+      </c>
+      <c r="B63" s="24">
+        <f t="shared" si="3"/>
+        <v>62</v>
       </c>
       <c r="C63" s="20"/>
-      <c r="D63" s="21" t="str">
+      <c r="D63" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E63" s="21" t="str">
+        <v>500</v>
+      </c>
+      <c r="E63" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F63" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G63" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H63" s="21" t="str">
+        <v>83.803765812124794</v>
+      </c>
+      <c r="F63" s="21">
+        <f t="shared" si="5"/>
+        <v>416.19623418787523</v>
+      </c>
+      <c r="G63" s="21">
+        <f t="shared" si="4"/>
+        <v>26494.166508023187</v>
+      </c>
+      <c r="H63" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>23505.833491976813</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64" s="2"/>
-      <c r="B64" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A64" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B64" s="23">
+        <f t="shared" si="3"/>
+        <v>63</v>
       </c>
       <c r="C64" s="3"/>
-      <c r="D64" s="4" t="str">
+      <c r="D64" s="4">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E64" s="4" t="str">
+        <v>500</v>
+      </c>
+      <c r="E64" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F64" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G64" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H64" s="4" t="str">
+        <v>82.50765501362342</v>
+      </c>
+      <c r="F64" s="4">
+        <f t="shared" si="5"/>
+        <v>417.49234498637657</v>
+      </c>
+      <c r="G64" s="4">
+        <f t="shared" si="4"/>
+        <v>26076.674163036809</v>
+      </c>
+      <c r="H64" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>23923.325836963191</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Angom_Bijenti_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Angom_Bijenti_Daily.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>28500</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>26076.674163036809</v>
+        <v>24816.380037149793</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>23923.325836963191</v>
+        <v>25183.619962850207</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -2747,87 +2747,93 @@
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" s="19"/>
-      <c r="B65" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A65" s="19">
+        <v>46289</v>
+      </c>
+      <c r="B65" s="24">
+        <f t="shared" si="3"/>
+        <v>64</v>
       </c>
       <c r="C65" s="20"/>
-      <c r="D65" s="21" t="str">
+      <c r="D65" s="21">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="E65" s="21" t="str">
+        <v>500</v>
+      </c>
+      <c r="E65" s="21">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F65" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G65" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H65" s="21" t="str">
+        <v>81.20750789027332</v>
+      </c>
+      <c r="F65" s="21">
+        <f t="shared" si="5"/>
+        <v>418.79249210972671</v>
+      </c>
+      <c r="G65" s="21">
+        <f t="shared" si="4"/>
+        <v>25657.881670927083</v>
+      </c>
+      <c r="H65" s="21">
         <f t="shared" si="8"/>
-        <v/>
+        <v>24342.118329072917</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" s="2"/>
-      <c r="B66" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A66" s="2">
+        <v>46290</v>
+      </c>
+      <c r="B66" s="23">
+        <f t="shared" si="3"/>
+        <v>65</v>
       </c>
       <c r="C66" s="3"/>
-      <c r="D66" s="4" t="str">
+      <c r="D66" s="4">
         <f t="shared" ref="D66:D97" si="9">IF(AND($A66&lt;&gt;"",$B66&lt;&gt;""),$K$9,"")</f>
-        <v/>
-      </c>
-      <c r="E66" s="4" t="str">
+        <v>500</v>
+      </c>
+      <c r="E66" s="4">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="F66" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G66" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H66" s="4" t="str">
+        <v>79.903311872224563</v>
+      </c>
+      <c r="F66" s="4">
+        <f t="shared" si="5"/>
+        <v>420.09668812777545</v>
+      </c>
+      <c r="G66" s="4">
+        <f t="shared" si="4"/>
+        <v>25237.784982799309</v>
+      </c>
+      <c r="H66" s="4">
         <f t="shared" si="8"/>
-        <v/>
+        <v>24762.215017200691</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" s="19"/>
-      <c r="B67" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A67" s="19">
+        <v>46294</v>
+      </c>
+      <c r="B67" s="24">
+        <f t="shared" si="3"/>
+        <v>66</v>
       </c>
       <c r="C67" s="20"/>
-      <c r="D67" s="21" t="str">
+      <c r="D67" s="21">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E67" s="21" t="str">
+        <v>500</v>
+      </c>
+      <c r="E67" s="21">
         <f t="shared" ref="E67:E98" si="10">IF(AND($A67&lt;&gt;"",$B67&lt;&gt;""),G66*$K$8,"")</f>
-        <v/>
-      </c>
-      <c r="F67" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G67" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H67" s="21" t="str">
+        <v>78.595054350482343</v>
+      </c>
+      <c r="F67" s="21">
+        <f t="shared" si="5"/>
+        <v>421.40494564951769</v>
+      </c>
+      <c r="G67" s="21">
+        <f t="shared" si="4"/>
+        <v>24816.380037149793</v>
+      </c>
+      <c r="H67" s="21">
         <f t="shared" ref="H67:H98" si="11">IF(AND($A67&lt;&gt;"",$B67&lt;&gt;""),$K$7-G67,"")</f>
-        <v/>
+        <v>25183.619962850207</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Angom_Bijenti_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Angom_Bijenti_Daily.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>27000</v>
+        <v>25500</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>24816.380037149793</v>
+        <v>23544.274850073471</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>25183.619962850207</v>
+        <v>26455.725149926529</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -2837,87 +2837,93 @@
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="2"/>
-      <c r="B68" s="23" t="str">
+      <c r="A68" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B68" s="23">
         <f t="shared" ref="B68:B121" si="12">IF(A68&lt;&gt;"",B67+1,"")</f>
-        <v/>
+        <v>67</v>
       </c>
       <c r="C68" s="3"/>
-      <c r="D68" s="4" t="str">
+      <c r="D68" s="4">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E68" s="4" t="str">
+        <v>500</v>
+      </c>
+      <c r="E68" s="4">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F68" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G68" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H68" s="4" t="str">
+        <v>77.282722676785184</v>
+      </c>
+      <c r="F68" s="4">
+        <f t="shared" si="5"/>
+        <v>422.71727732321483</v>
+      </c>
+      <c r="G68" s="4">
+        <f t="shared" si="4"/>
+        <v>24393.662759826577</v>
+      </c>
+      <c r="H68" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>25606.337240173423</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A69" s="19"/>
-      <c r="B69" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A69" s="19">
+        <v>46302</v>
+      </c>
+      <c r="B69" s="24">
+        <f t="shared" si="12"/>
+        <v>68</v>
       </c>
       <c r="C69" s="20"/>
-      <c r="D69" s="21" t="str">
+      <c r="D69" s="21">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E69" s="21" t="str">
+        <v>500</v>
+      </c>
+      <c r="E69" s="21">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F69" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G69" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H69" s="21" t="str">
+        <v>75.966304163482647</v>
+      </c>
+      <c r="F69" s="21">
+        <f t="shared" si="5"/>
+        <v>424.03369583651738</v>
+      </c>
+      <c r="G69" s="21">
+        <f t="shared" si="4"/>
+        <v>23969.629063990058</v>
+      </c>
+      <c r="H69" s="21">
         <f t="shared" si="11"/>
-        <v/>
+        <v>26030.370936009942</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" s="2"/>
-      <c r="B70" s="23" t="str">
-        <f t="shared" si="12"/>
-        <v/>
+      <c r="A70" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B70" s="23">
+        <f t="shared" si="12"/>
+        <v>69</v>
       </c>
       <c r="C70" s="3"/>
-      <c r="D70" s="4" t="str">
+      <c r="D70" s="4">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E70" s="4" t="str">
+        <v>500</v>
+      </c>
+      <c r="E70" s="4">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="F70" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G70" s="4" t="str">
+        <v>74.645786083412588</v>
+      </c>
+      <c r="F70" s="4">
+        <f t="shared" si="5"/>
+        <v>425.35421391658741</v>
+      </c>
+      <c r="G70" s="4">
         <f t="shared" ref="G70:G121" si="13">IF(AND($A70&lt;&gt;"",$B70&lt;&gt;""),G69-F70,"")</f>
-        <v/>
-      </c>
-      <c r="H70" s="4" t="str">
+        <v>23544.274850073471</v>
+      </c>
+      <c r="H70" s="4">
         <f t="shared" si="11"/>
-        <v/>
+        <v>26455.725149926529</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
